--- a/workspace-backup/Backend_Role_Alert_Filter_Check.xlsx
+++ b/workspace-backup/Backend_Role_Alert_Filter_Check.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All 2026 Subcategories" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Roles to Review'!$A$1:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Roles to Review'!$A$1:$I$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
       <sz val="10"/>
     </font>
     <font>
@@ -122,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,19 +136,25 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,11 +520,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B16"/>
+  <dimension ref="B2:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="118" customWidth="1" min="2" max="2"/>
+    <col width="122" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -529,14 +540,14 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sashka - this is the list of every tech-ish role our clients opened since 1 April 2026.</t>
+          <t>Sashka - every tech role our clients opened between 2 April and 23 August 2026. 161 of them.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mark column G 'Yes' for any role you would want a Slack message about, 'No' for the rest.</t>
+          <t>Mark column H 'Yes' for any role you would want a Slack message about, 'No' for the rest.</t>
         </is>
       </c>
     </row>
@@ -553,28 +564,28 @@
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Why we are asking instead of just filtering on 'Backend':</t>
+          <t>Why we are asking instead of just filtering on the Backend tag:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Row 40 and 43: two Salesforce Developer roles are tagged Full Stack and Android. Probably not what you want.</t>
+          <t>Rows 40, 41, 42, 43: Salesforce Developer roles tagged Full Stack and Android. Probably not what you want.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Row 22 and 64: Platform Engineer, Event Streaming and Senior Software Engineer are tagged Not apply. A Backend-only filter misses both.</t>
+          <t>Rows 21, 70, 102: real platform and software engineering roles tagged 'Not apply'. A Backend-only filter misses them.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>So the tag alone is not enough. Your Yes/No answers tell us which tags to trust and which titles to catch by name.</t>
+          <t>The tag alone is wrong in both directions. Your answers tell us which tags to trust and which titles to catch by name.</t>
         </is>
       </c>
     </row>
@@ -584,24 +595,31 @@
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tab 2 lists every subcategory our clients used in 2026 with a count, if you would rather pick whole buckets.</t>
+          <t>Column G says whether the role is still open. Archived ones are here so you can judge the pattern, not to act on.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tab 3 lists every subcategory our clients used in 2026 with a count, if you would rather pick whole buckets.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Scope: client roles only. Test, internal Tribe and BD pipelines are already excluded.</t>
-        </is>
-      </c>
+      <c r="B15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Source: Bubble jobs data via the recruiting warehouse. Pulled 25 Aug 2026.</t>
+          <t>Scope: client roles only. Test, internal Tribe and BD pipelines are already excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Source: Bubble jobs data via the recruiting warehouse. Pulled 26 Aug 2026.</t>
         </is>
       </c>
     </row>
@@ -616,17 +634,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -662,10 +681,15 @@
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
           <t>Alert me? (Yes/No)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Notes (optional)</t>
         </is>
@@ -684,7 +708,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Member of Technical Staff (Machine Learning)</t>
+          <t>Member of Technical Staff (Fullstack)</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -694,7 +718,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning / AI</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -702,8 +726,13 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G2" s="7" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -718,7 +747,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Member of Technical Staff (Fullstack)</t>
+          <t>Member of Technical Staff (Machine Learning)</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -728,7 +757,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Machine Learning / AI</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -736,8 +765,13 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -770,8 +804,13 @@
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -804,8 +843,13 @@
           <t>New York, NY, USA</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -838,8 +882,13 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -872,76 +921,91 @@
           <t>Schoenefeld, Germany</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>EM Platform - AVIV - Sequence R/O</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Engineering Management</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Senior Backend Engineer - AVIV - Sequence R/O - AVIV</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -956,7 +1020,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Staff Backend Engineer Trust &amp; Safety - AVIV - Sequence R/O</t>
+          <t>Platform QA Engineer (Croatia)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -966,16 +1030,21 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -990,7 +1059,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Platform QA Engineer (Croatia)</t>
+          <t>Senior IOS Engineer (Romania)</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1000,50 +1069,60 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Automation QA</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n"/>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Senior IOS Engineer (Romania)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>iOS</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Bucharest, Romania</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer Trust &amp; Safety - AVIV - Sequence R/O</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1076,8 +1155,13 @@
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1110,42 +1194,52 @@
           <t>New York, NY, USA</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Senior Android Engineer Croatia - Aviv</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Android</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Belgium - Kristina</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Management</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1160,7 +1254,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Engineering Manager, Belgium - Kristina</t>
+          <t>Senior Android Engineer Croatia - Aviv</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1170,16 +1264,21 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Engineering Management</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n"/>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1212,8 +1311,13 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1246,42 +1350,52 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Glovo</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Product Data Analytics Intern</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1314,8 +1428,13 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1330,7 +1449,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Staff Mobile engineer</t>
+          <t>Platform Engineer, Event Streaming</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1340,16 +1459,21 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Not apply</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n"/>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1364,7 +1488,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Platform Engineer, Event Streaming</t>
+          <t>Staff Mobile engineer</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1374,50 +1498,60 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Not apply</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Context Inteligence Team</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Taxfix</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Technical Product Manager</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Product Management</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Product Manager</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="n"/>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1427,12 +1561,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Taxfix</t>
+          <t>Parloa</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>IT System Admin/Engineer</t>
+          <t>SAP Integration Architect EMEA</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1442,16 +1576,21 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1461,12 +1600,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Parloa</t>
+          <t>Taxfix</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>SAP Integration Architect EMEA</t>
+          <t>IT System Admin/Engineer</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1476,16 +1615,21 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1518,8 +1662,13 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1529,31 +1678,36 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Parloa</t>
+          <t>Taxfix</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager - Context Inteligence Team</t>
+          <t>Technical Product Manager</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n"/>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1586,8 +1740,13 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1620,42 +1779,52 @@
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Glovo</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>L1 Tech Support</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Systems Admin</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1688,42 +1857,52 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Parloa</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Senior Engineer - Filip</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n"/>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1738,26 +1917,31 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>QA Automation Contractor (France)</t>
+          <t>Finops Engineer</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (DevOps / SRE)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Automation QA</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="n"/>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1772,26 +1956,31 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Finops Engineer</t>
+          <t>QA Automation Contractor (France)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Engineering (DevOps / SRE)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n"/>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1806,7 +1995,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Product Manager Ads</t>
+          <t>Head of PM Fintech</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1824,8 +2013,13 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n"/>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1840,7 +2034,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Head of PM Fintech</t>
+          <t>Product Manager Ads</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,8 +2052,13 @@
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1892,178 +2091,208 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Recontacting: EM France - AVIV</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Recontacting: Senior IOS Engineer - Paris - AVIV</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n"/>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Salesforce Developer</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Full Stack</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>Albania</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n"/>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Parloa</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Internal Platform</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="n"/>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Salesforce Developer</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Eucalyptus</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="n"/>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Salesforce Developer</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -2096,8 +2325,13 @@
           <t>Zagreb, Croatia</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2107,56 +2341,61 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Reaktor</t>
+          <t>Eucalyptus</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer | Helsinki</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Data &amp; Analytics</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Helsinki, Finland</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="n"/>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Taxfix</t>
+          <t>Parloa</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>AI Builder</t>
+          <t>Senior Data Engineer - Internal Platform</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Not apply</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -2164,13 +2403,18 @@
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2180,7 +2424,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer | Amsterdam</t>
+          <t>Senior Fullstack Engineer | Helsinki</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -2195,11 +2439,16 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Amsterdam, Netherlands</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="n"/>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -2209,31 +2458,36 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Wolt</t>
+          <t>Reaktor</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Store Team Lead (WM), Budapest, Q3 2026</t>
+          <t>Senior Fullstack Engineer | Amsterdam</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Non-Tech</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Budapest, Hungary</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="n"/>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2266,446 +2520,516 @@
           <t>Lisbon, Portugal</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Taxfix</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>AI Builder</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Store Team Lead (WM), Budapest, Q3 2026</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Budapest, Hungary</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Store Manager - Astana</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Non-Tech</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>Astana, Kazakhstan</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - Bucharest, Romania</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Bucharest, Romania</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Manager Platform - Berlin</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>Engineering Manager Platform - Berlin</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Engineering (Engineering Management)</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>Not apply</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Product Director</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Product Manager Berlin, Aviv</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>AVIV</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Product Director</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Product Management</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Product Manager</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>AVIV</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>Product Manager Berlin, Aviv</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Product Management</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>Product Manager</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Wolt</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Support Team Lead Italian speaker, Albania</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Non-Tech</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Albania</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>AVIV</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>Head of Engineering, Berlin AVIV</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Engineering (Engineering Management)</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>Not apply</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="n"/>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Support Team Lead Italian speaker, Albania</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>AVIV</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Head of Engineering, Berlin AVIV</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Senior Backend Engineer - France</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>QA Engineer, Automation</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Automation / Manual QA)</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>QA Test Automation</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>Upvest</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Wolt</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Sr CRM Designer</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>AVIV</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>QA Engineer, Automation</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Engineering (Automation / Manual QA)</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>QA Test Automation</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Upvest</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="n"/>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Upvest</t>
+          <t>Wolt</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr CRM Designer</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Prague, Czechia</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="n"/>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -2715,31 +3039,36 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>AVIV</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Senior Product Data Scientist</t>
+          <t>QA Engineer Automation - Croatia - Kristina</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Automation QA</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Barcelona, Spain</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="n"/>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -2749,257 +3078,3915 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Junior Analytics Engineer - AI &amp; Data Enablement</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Senior Product Data Scientist</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
           <t>SevenRooms</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Front end developer</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Upvest</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Lisbon, Portugal</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Upvest</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Prague, Czechia</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Upvest</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Upvest</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Sr SWE (Platform &amp; Infra) - Helsinki</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Sr SWE (Platform &amp; Infra) - Israel</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Israel</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Confidential - Belgium</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Executive Assistant, Berlin AVIV</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer Paris - Aviv</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Backend Engineer Wolt+</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Manager Platform, Berlin (Wlad)</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>GSI Partnerships Manager</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>New York, NY, USA</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Senior Android Engineer Germany - Lejla</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Romania (Contractor) Kristina</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Store Manager (WM Distribution Center), Hungary, Q2 2026</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Budapest, Hungary</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Junior Backend Developer - France</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Store Manager - Berlin</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Android platform dev</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Store Team Lead, Croatia, Q2 2026</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Zagreb, Croatia</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Store Team Lead, Szeged, Hungary Q2 26</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Szeged, Hungary</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Category Manager - Greece</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr"/>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Senior Front End Engineer (DE) - Alex</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer - DE</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>SAP Integration Engineer</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Senior Go Dev Data Group</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Platform - Berlin</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Management</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Manager Trust &amp; Safety, Berlin (Wlad)</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Content Associate - Baku</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>Baku, Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Frontend Engineer - Croatia</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Croatia</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Category Manager, Czechia, Q2 2026</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Prague, Czechia</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Director, Consumer pricing</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Sr Platform Engineer - Contractor</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>Glovo</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>Junior Analytics Engineer - AI &amp; Data Enablement</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>iOS Engineer - IC4 (Sam)</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>QA Automation - Authentication, Croatia</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Automation QA</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>QA Automation - Financing, Croatia</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Automation / Manual QA)</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>QA Test Automation</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Cloud Security Engineer</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer - Australia / India</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Product Manager, Lead AVIV Berlin</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer - ClickHouse (Germany)</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="n"/>
+      <c r="I109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Manager France, Kristina</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Manager T&amp;S Kristina, Berlin</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Fullstack .NET (Bucharest)</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Fullstack React (Bucharest)</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Taxfix</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Senior Marketing Data Analyst</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>Nexi</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Supporting other TAs</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>Applied Scientist</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>Go/ Python I4</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Platform Team - Berlin (Kristina)</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Platform Team - Berlin (Wlad)</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>Taxfix</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Engineer - Stuttgart</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>70 Stuttgart, Germany</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>FTAPI</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Lead Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="n"/>
+      <c r="I122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Head of Partnerships</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="n"/>
+      <c r="I123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Front End Engineer (Paris)</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="n"/>
+      <c r="I124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Taxfix</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Software Engineer - FullStack</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="n"/>
+      <c r="I125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Store Manager (Bergen)</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Bergen, Norway</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="n"/>
+      <c r="I126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Store Manager (WM), Turku Finland, Q2 2026</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>Turku, Finland</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="n"/>
+      <c r="I127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Senior Android Engineer - Germany [ ALEX ]</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer Python</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="n"/>
+      <c r="I129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Senior iOS Engineer - Germany [ ALEX ]</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="n"/>
+      <c r="I130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Category Manager (WM), Croatia</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>Zagreb, Croatia</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Category Manager (WM), Slovenia</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>Ljubljana, Slovenia</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="n"/>
+      <c r="I132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Director, Platforms</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="n"/>
+      <c r="I133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>VP of Product</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="n"/>
+      <c r="I134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Senior Android Engineer - Croatia (Alex)</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="n"/>
+      <c r="I135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Senior IOS Engineer - Croatia</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>iOS Engineer IC2 (Chene)</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="n"/>
+      <c r="I137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>iOS Engineer IC3 (Chene)</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="n"/>
+      <c r="I138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>Taxfix</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Working Student Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Adminstrator</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>IT &amp; Technical Support</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce Developer</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>New York, NY, USA</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="n"/>
+      <c r="I140" s="7" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>Senior Staff Engineer</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="n"/>
+      <c r="I141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>Manager, Technical Writing</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="n"/>
+      <c r="I142" s="7" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>Fullstack Developer Backend Focused</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="n"/>
+      <c r="I143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Fullstack Developer Frontend Focused</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="n"/>
+      <c r="I144" s="7" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Store Manager (WM), Budapest, Q2 2026</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>Budapest, Hungary</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="n"/>
+      <c r="I145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Inside Sales Solution Architect - Banglore, Karnataka</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>IT &amp; Technical Support</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="n"/>
+      <c r="I146" s="7" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Finland)</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="n"/>
+      <c r="I147" s="7" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Aiven</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Israel)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo, Israel</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="n"/>
+      <c r="I148" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>Category Manager - Cyprus</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>Nicosia, Cyprus</t>
+        </is>
+      </c>
+      <c r="G149" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="n"/>
+      <c r="I149" s="7" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>Enam</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer - Email sequence</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="n"/>
+      <c r="I150" s="7" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Quandoo Germany Pool</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="n"/>
+      <c r="I151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Principal Quality engineer</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>Engineering (Automation / Manual QA)</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>QA Test Automation</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Brussels, Belgium</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="n"/>
+      <c r="I152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Product Manager Demand (AVIV)</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F153" s="10" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="n"/>
+      <c r="I153" s="7" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Product Manager Supply (AVIV)</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="n"/>
+      <c r="I154" s="7" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>PhantomBuster</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Product Expert - Customer Care Agent</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>Non-Tech</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="n"/>
+      <c r="I155" s="7" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer Trust &amp; Safety - Kristina - Berlin</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H156" s="7" t="n"/>
+      <c r="I156" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer Trust &amp; Safety - Wlad - Berlin</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="n"/>
+      <c r="I157" s="7" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer Trust &amp; Safety - Kristina - Berlin</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="n"/>
+      <c r="I158" s="7" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>AVIV</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Staff Backend Engineer Trust &amp; Safety - Wlad - Berlin</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F159" s="10" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="n"/>
+      <c r="I159" s="7" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Data Internship</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
         <is>
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Upvest</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>Lisbon, Portugal</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>AVIV</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>QA Engineer Automation - Croatia - Kristina</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Automation QA</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="n"/>
+      <c r="I160" s="7" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>Glovo</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Frontend Engineer - L1</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr">
         <is>
           <t>Barcelona, Spain</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Aiven</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>Sr SWE (Platform &amp; Infra) - Helsinki</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>Helsinki, Finland</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-    </row>
-    <row r="71">
-      <c r="F71" s="9" t="inlineStr">
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>Taxfix</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Director IT</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>Engineering (Engineering Management)</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>Not apply</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="n"/>
+      <c r="I162" s="7" t="n"/>
+    </row>
+    <row r="164">
+      <c r="F164" s="11" t="inlineStr">
         <is>
           <t>Roles listed:</t>
         </is>
       </c>
-      <c r="G71" s="10" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>Yellow cells are the only ones to fill in. Use the filter on row 1 to work through them by category.</t>
+      <c r="G164" s="12" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="C166" s="13" t="inlineStr">
+        <is>
+          <t>Yellow cells are the only ones to fill in. Grey rows are archived roles. Use the filter on row 1 to work through by category.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H69"/>
+  <autoFilter ref="A1:I162"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3045,675 +7032,675 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="14" t="n">
         <v>54</v>
       </c>
       <c r="D2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="15" t="n">
         <v>23</v>
       </c>
       <c r="D3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Full Stack</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="14" t="n">
         <v>19</v>
       </c>
       <c r="D4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="15" t="n">
         <v>19</v>
       </c>
       <c r="D5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="15" t="n">
         <v>9</v>
       </c>
       <c r="D7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Engineering Management</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="15" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="14" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Automation QA</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="15" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Android</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="14" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Machine Learning / AI</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>iOS</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Embedded</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>DevOps / SRE</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Engineering (Automation / Manual QA)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>QA Test Automation</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="14" t="n">
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Engineering (DevOps / SRE)</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Engineering (DevOps / SRE)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="15" t="n">
         <v>19</v>
       </c>
       <c r="D21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Applications</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Data Infrastructure</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Engineering (Engineering Management)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="15" t="n">
         <v>17</v>
       </c>
       <c r="D27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="14" t="n">
         <v>6</v>
       </c>
       <c r="D28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Analytics Engineer</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Business Operations</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Solutions Architect</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Technical Support Engineer</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Systems Admin</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Solutions Architecture</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>Database Administrator</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>IT &amp; Technical Support</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Salesforce Developer</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Product Management</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="15" t="n">
         <v>19</v>
       </c>
       <c r="D39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Product Management</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>Not apply</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="15" t="n">
         <v>4</v>
       </c>
       <c r="D41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>Non-Tech</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="14" t="n">
         <v>68</v>
       </c>
       <c r="D42" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>Total roles listed:</t>
         </is>
       </c>
-      <c r="C44" s="14" t="n">
+      <c r="C44" s="16" t="n">
         <v>326</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Counts are client roles opened 1 Jan - 25 Aug 2026, test/internal/BD excluded. 'Other / Non-Tech' shown for completeness.</t>
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>Counts are client roles opened 1 Jan to 25 Aug 2026, test/internal/BD excluded. 'Other / Non-Tech' shown for completeness.</t>
         </is>
       </c>
     </row>
